--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/105.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/105.xlsx
@@ -426,13 +426,13 @@
         <v>-1.262372991294073</v>
       </c>
       <c r="E2">
-        <v>-9.695723050148274</v>
+        <v>-8.25951751861562</v>
       </c>
       <c r="F2">
-        <v>-3.724107218993898</v>
+        <v>-3.926792983478284</v>
       </c>
       <c r="G2">
-        <v>-7.710702014187651</v>
+        <v>-6.739348226419014</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.166807199013447</v>
       </c>
       <c r="E3">
-        <v>-10.74504746178363</v>
+        <v>-9.672138757516327</v>
       </c>
       <c r="F3">
-        <v>-3.71030993153287</v>
+        <v>-3.962976071632566</v>
       </c>
       <c r="G3">
-        <v>-6.336749472842706</v>
+        <v>-7.38324933380726</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.053349732171663</v>
       </c>
       <c r="E4">
-        <v>-11.59086225151427</v>
+        <v>-9.853803020808032</v>
       </c>
       <c r="F4">
-        <v>-3.54609272086709</v>
+        <v>-3.871936008962693</v>
       </c>
       <c r="G4">
-        <v>-7.054051995927672</v>
+        <v>-6.911681985011315</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.9252648891069974</v>
       </c>
       <c r="E5">
-        <v>-12.42544189723189</v>
+        <v>-10.80788456711406</v>
       </c>
       <c r="F5">
-        <v>-3.657340806328258</v>
+        <v>-4.215359738447908</v>
       </c>
       <c r="G5">
-        <v>-6.58524233156594</v>
+        <v>-6.466675143076943</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.7754806639708994</v>
       </c>
       <c r="E6">
-        <v>-12.13861741053406</v>
+        <v>-12.77167543443634</v>
       </c>
       <c r="F6">
-        <v>-3.256295011936905</v>
+        <v>-3.772941134123735</v>
       </c>
       <c r="G6">
-        <v>-6.167077392863979</v>
+        <v>-6.528367159201261</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.600141624617108</v>
       </c>
       <c r="E7">
-        <v>-14.04009194703679</v>
+        <v>-12.30829480312747</v>
       </c>
       <c r="F7">
-        <v>-3.687811472872835</v>
+        <v>-3.663417709595195</v>
       </c>
       <c r="G7">
-        <v>-6.585384685024129</v>
+        <v>-6.713261127569557</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.397359414095287</v>
       </c>
       <c r="E8">
-        <v>-15.54541104887451</v>
+        <v>-13.87425922887591</v>
       </c>
       <c r="F8">
-        <v>-3.706091056350412</v>
+        <v>-3.563174485080219</v>
       </c>
       <c r="G8">
-        <v>-6.176439615649038</v>
+        <v>-6.028405261314988</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.1649818542015049</v>
       </c>
       <c r="E9">
-        <v>-15.07632906878998</v>
+        <v>-14.81380437361731</v>
       </c>
       <c r="F9">
-        <v>-3.725552720111784</v>
+        <v>-3.538211633396856</v>
       </c>
       <c r="G9">
-        <v>-6.51084113111636</v>
+        <v>-6.587427291621859</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.09933238368145182</v>
       </c>
       <c r="E10">
-        <v>-15.45036743640153</v>
+        <v>-15.66703227529852</v>
       </c>
       <c r="F10">
-        <v>-3.521080995506962</v>
+        <v>-3.197459388785668</v>
       </c>
       <c r="G10">
-        <v>-5.544910016941048</v>
+        <v>-5.334524847920364</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.3916984938939773</v>
       </c>
       <c r="E11">
-        <v>-17.83209569836571</v>
+        <v>-16.38293420269711</v>
       </c>
       <c r="F11">
-        <v>-3.479733864963627</v>
+        <v>-3.494289108598217</v>
       </c>
       <c r="G11">
-        <v>-5.76230030032283</v>
+        <v>-5.36938489244889</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.70699615911306</v>
       </c>
       <c r="E12">
-        <v>-17.84561772175262</v>
+        <v>-16.70714577080227</v>
       </c>
       <c r="F12">
-        <v>-3.290574511799555</v>
+        <v>-3.388462687788372</v>
       </c>
       <c r="G12">
-        <v>-4.64037628033706</v>
+        <v>-5.517187508595192</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.036543758413205</v>
       </c>
       <c r="E13">
-        <v>-19.39622156366704</v>
+        <v>-17.27536510386272</v>
       </c>
       <c r="F13">
-        <v>-2.931276777774491</v>
+        <v>-3.42296667521718</v>
       </c>
       <c r="G13">
-        <v>-3.922150115046637</v>
+        <v>-4.42629654249455</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.363635050335779</v>
       </c>
       <c r="E14">
-        <v>-18.63413372986421</v>
+        <v>-18.47455483430791</v>
       </c>
       <c r="F14">
-        <v>-3.167568579423051</v>
+        <v>-2.969103346855928</v>
       </c>
       <c r="G14">
-        <v>-3.528774541342738</v>
+        <v>-4.445812208448554</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.670916830689085</v>
       </c>
       <c r="E15">
-        <v>-21.28666020901307</v>
+        <v>-19.08413272048042</v>
       </c>
       <c r="F15">
-        <v>-3.485511727598154</v>
+        <v>-3.076702473907764</v>
       </c>
       <c r="G15">
-        <v>-3.472674036634249</v>
+        <v>-3.679381189560802</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.942520547101865</v>
       </c>
       <c r="E16">
-        <v>-21.25038713221164</v>
+        <v>-20.53868762869216</v>
       </c>
       <c r="F16">
-        <v>-2.948665037926656</v>
+        <v>-3.086082906377066</v>
       </c>
       <c r="G16">
-        <v>-3.090772813769464</v>
+        <v>-3.629388641372268</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.163106260208625</v>
       </c>
       <c r="E17">
-        <v>-21.76118088638082</v>
+        <v>-20.56494824946263</v>
       </c>
       <c r="F17">
-        <v>-2.860807562818338</v>
+        <v>-2.794438766506041</v>
       </c>
       <c r="G17">
-        <v>-2.744188490717624</v>
+        <v>-2.79272108832334</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.324354930669399</v>
       </c>
       <c r="E18">
-        <v>-23.44782008748566</v>
+        <v>-22.4026211156713</v>
       </c>
       <c r="F18">
-        <v>-2.593436244584144</v>
+        <v>-2.406582237902062</v>
       </c>
       <c r="G18">
-        <v>-2.081235193750873</v>
+        <v>-2.226323162554972</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.424553976048677</v>
       </c>
       <c r="E19">
-        <v>-23.39105566579951</v>
+        <v>-22.14389128171706</v>
       </c>
       <c r="F19">
-        <v>-2.175128101885853</v>
+        <v>-2.319870394911816</v>
       </c>
       <c r="G19">
-        <v>-2.497999771689722</v>
+        <v>-2.905614001758027</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.464914021912139</v>
       </c>
       <c r="E20">
-        <v>-24.50626031729846</v>
+        <v>-23.70372415365911</v>
       </c>
       <c r="F20">
-        <v>-1.859856438584777</v>
+        <v>-2.282012347869073</v>
       </c>
       <c r="G20">
-        <v>-0.9585265744722956</v>
+        <v>-1.634453899407451</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.451425425958079</v>
       </c>
       <c r="E21">
-        <v>-25.19116484011455</v>
+        <v>-24.34415906171989</v>
       </c>
       <c r="F21">
-        <v>-1.794129627009651</v>
+        <v>-1.796316516953041</v>
       </c>
       <c r="G21">
-        <v>-1.257233787935196</v>
+        <v>-1.842577965824813</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.392877025812561</v>
       </c>
       <c r="E22">
-        <v>-25.49883842114369</v>
+        <v>-24.72469578953244</v>
       </c>
       <c r="F22">
-        <v>-1.770776293189927</v>
+        <v>-1.800903187262342</v>
       </c>
       <c r="G22">
-        <v>-1.334101344811533</v>
+        <v>-1.292385160471177</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.297881754796059</v>
       </c>
       <c r="E23">
-        <v>-25.1645691122675</v>
+        <v>-24.38002457586063</v>
       </c>
       <c r="F23">
-        <v>-1.973074381729803</v>
+        <v>-1.551140474909458</v>
       </c>
       <c r="G23">
-        <v>-0.3762380301154258</v>
+        <v>-1.526308308276079</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.174140483750112</v>
       </c>
       <c r="E24">
-        <v>-25.82677692335715</v>
+        <v>-25.53225403084629</v>
       </c>
       <c r="F24">
-        <v>-1.381882648597643</v>
+        <v>-1.093981901019869</v>
       </c>
       <c r="G24">
-        <v>-1.098281254412629</v>
+        <v>-1.499204871946066</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.027803677251541</v>
       </c>
       <c r="E25">
-        <v>-26.3851332400289</v>
+        <v>-25.6214694972714</v>
       </c>
       <c r="F25">
-        <v>-1.096283934032249</v>
+        <v>-0.8178066940287224</v>
       </c>
       <c r="G25">
-        <v>-1.130211466138899</v>
+        <v>-1.825409476658152</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.864864012042818</v>
       </c>
       <c r="E26">
-        <v>-27.45994843185343</v>
+        <v>-25.72960945657457</v>
       </c>
       <c r="F26">
-        <v>-0.9311820269802796</v>
+        <v>-0.8146116809561248</v>
       </c>
       <c r="G26">
-        <v>-1.071283755539872</v>
+        <v>-1.737954795147225</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.688989376152267</v>
       </c>
       <c r="E27">
-        <v>-26.59936628838377</v>
+        <v>-25.78087631081541</v>
       </c>
       <c r="F27">
-        <v>-0.7467360843381361</v>
+        <v>-0.7690829517634583</v>
       </c>
       <c r="G27">
-        <v>-1.238410025998899</v>
+        <v>-2.233970522750688</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.50172579785958</v>
       </c>
       <c r="E28">
-        <v>-27.47952049651458</v>
+        <v>-25.97791474336315</v>
       </c>
       <c r="F28">
-        <v>-1.102775021000586</v>
+        <v>-1.038038108471805</v>
       </c>
       <c r="G28">
-        <v>-1.703687338270229</v>
+        <v>-2.251321091922008</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.306441573159604</v>
       </c>
       <c r="E29">
-        <v>-27.04112798478003</v>
+        <v>-26.14827593553171</v>
       </c>
       <c r="F29">
-        <v>-0.7271186875050382</v>
+        <v>-0.8729668510137387</v>
       </c>
       <c r="G29">
-        <v>-1.337011314340553</v>
+        <v>-2.605973214453052</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.105922109822188</v>
       </c>
       <c r="E30">
-        <v>-27.06853430947445</v>
+        <v>-25.32432008983609</v>
       </c>
       <c r="F30">
-        <v>-0.700400525295143</v>
+        <v>-0.6438164047447144</v>
       </c>
       <c r="G30">
-        <v>-2.686644588154012</v>
+        <v>-1.929072589129351</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.9024866689663501</v>
       </c>
       <c r="E31">
-        <v>-26.69906064366263</v>
+        <v>-25.51222459031036</v>
       </c>
       <c r="F31">
-        <v>-0.9334500969291446</v>
+        <v>-0.6339696014276366</v>
       </c>
       <c r="G31">
-        <v>-2.483347297132908</v>
+        <v>-2.773990021662143</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.7023253482082846</v>
       </c>
       <c r="E32">
-        <v>-25.83650861399964</v>
+        <v>-24.97861185561653</v>
       </c>
       <c r="F32">
-        <v>-1.034384179858056</v>
+        <v>-0.560941559564235</v>
       </c>
       <c r="G32">
-        <v>-1.586007375985756</v>
+        <v>-3.01461702418407</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.5121155676538363</v>
       </c>
       <c r="E33">
-        <v>-25.62066795737205</v>
+        <v>-25.08410265762521</v>
       </c>
       <c r="F33">
-        <v>-0.5548099840487131</v>
+        <v>-0.4788072748418584</v>
       </c>
       <c r="G33">
-        <v>-2.179098230437268</v>
+        <v>-2.968077374992995</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.3382601709040765</v>
       </c>
       <c r="E34">
-        <v>-26.20648946890031</v>
+        <v>-24.40285714180731</v>
       </c>
       <c r="F34">
-        <v>-0.7955666859983613</v>
+        <v>-0.5946345753057021</v>
       </c>
       <c r="G34">
-        <v>-2.61910945915288</v>
+        <v>-3.173317956245651</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.1894042300664728</v>
       </c>
       <c r="E35">
-        <v>-24.90245197975553</v>
+        <v>-23.95027692100673</v>
       </c>
       <c r="F35">
-        <v>-0.6405327563600171</v>
+        <v>-0.7278037473471534</v>
       </c>
       <c r="G35">
-        <v>-3.719465274950298</v>
+        <v>-3.316747341734576</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.07252510988297364</v>
       </c>
       <c r="E36">
-        <v>-24.53169675579954</v>
+        <v>-23.86875986039465</v>
       </c>
       <c r="F36">
-        <v>-1.083648017669945</v>
+        <v>-0.6884819751036636</v>
       </c>
       <c r="G36">
-        <v>-2.638214617460014</v>
+        <v>-3.964415849946513</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.007097891550789436</v>
       </c>
       <c r="E37">
-        <v>-24.14381031467254</v>
+        <v>-22.72086415503434</v>
       </c>
       <c r="F37">
-        <v>-0.7158537191943677</v>
+        <v>-0.8057398660721421</v>
       </c>
       <c r="G37">
-        <v>-3.269823669260946</v>
+        <v>-3.883466390420253</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.04454444032211827</v>
       </c>
       <c r="E38">
-        <v>-22.91370469217697</v>
+        <v>-22.64218644762508</v>
       </c>
       <c r="F38">
-        <v>-0.9160560382051607</v>
+        <v>-0.3096621064968245</v>
       </c>
       <c r="G38">
-        <v>-2.931184655503357</v>
+        <v>-4.552987809736919</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.03865827347900591</v>
       </c>
       <c r="E39">
-        <v>-22.72588623270885</v>
+        <v>-22.19797484679066</v>
       </c>
       <c r="F39">
-        <v>-0.8964900001510363</v>
+        <v>-0.7706841859530698</v>
       </c>
       <c r="G39">
-        <v>-3.238843584104446</v>
+        <v>-3.934879162645135</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.009179950063681823</v>
       </c>
       <c r="E40">
-        <v>-22.79733196712786</v>
+        <v>-21.16763832666948</v>
       </c>
       <c r="F40">
-        <v>-0.8310854234955986</v>
+        <v>-0.9199791862248191</v>
       </c>
       <c r="G40">
-        <v>-3.431590166491894</v>
+        <v>-4.243683540002812</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.09531476862208432</v>
       </c>
       <c r="E41">
-        <v>-20.11811466217778</v>
+        <v>-20.96498458635222</v>
       </c>
       <c r="F41">
-        <v>-0.9921722337461988</v>
+        <v>-0.6349893217004827</v>
       </c>
       <c r="G41">
-        <v>-3.717012160705698</v>
+        <v>-3.951272984155606</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.2122133468065394</v>
       </c>
       <c r="E42">
-        <v>-21.26113772950585</v>
+        <v>-19.73242000247049</v>
       </c>
       <c r="F42">
-        <v>-1.042556852654076</v>
+        <v>-0.8551743475690081</v>
       </c>
       <c r="G42">
-        <v>-3.503495215604864</v>
+        <v>-3.699827118811341</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.3520934793724803</v>
       </c>
       <c r="E43">
-        <v>-21.30543526224888</v>
+        <v>-19.36968017750808</v>
       </c>
       <c r="F43">
-        <v>-1.504931656079093</v>
+        <v>-0.8386865227836868</v>
       </c>
       <c r="G43">
-        <v>-3.416143161005654</v>
+        <v>-3.81897696331525</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5066226855088806</v>
       </c>
       <c r="E44">
-        <v>-19.70736395578605</v>
+        <v>-18.57799876606513</v>
       </c>
       <c r="F44">
-        <v>-1.206355737781442</v>
+        <v>-0.8263455052167797</v>
       </c>
       <c r="G44">
-        <v>-3.326215501976892</v>
+        <v>-4.068433190790413</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.6665260267824916</v>
       </c>
       <c r="E45">
-        <v>-18.6920438554743</v>
+        <v>-17.12415029979859</v>
       </c>
       <c r="F45">
-        <v>-0.8875345201593708</v>
+        <v>-0.8023203654333857</v>
       </c>
       <c r="G45">
-        <v>-2.037241354079498</v>
+        <v>-3.898595583534723</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.8253011040570148</v>
       </c>
       <c r="E46">
-        <v>-17.84365689250729</v>
+        <v>-16.65446150419703</v>
       </c>
       <c r="F46">
-        <v>-0.9790749167405358</v>
+        <v>-0.7893323929248922</v>
       </c>
       <c r="G46">
-        <v>-2.37491037799408</v>
+        <v>-3.706766022261654</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.9769540508780863</v>
       </c>
       <c r="E47">
-        <v>-16.66777974625359</v>
+        <v>-16.06028948659862</v>
       </c>
       <c r="F47">
-        <v>-1.148771777775834</v>
+        <v>-1.006469026751115</v>
       </c>
       <c r="G47">
-        <v>-2.720491605747521</v>
+        <v>-4.090428455353331</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.114991341579179</v>
       </c>
       <c r="E48">
-        <v>-16.52309953018253</v>
+        <v>-15.63385667471832</v>
       </c>
       <c r="F48">
-        <v>-0.31262269159443</v>
+        <v>-1.086708006855887</v>
       </c>
       <c r="G48">
-        <v>-3.087985334425398</v>
+        <v>-4.121756147791454</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.23536970973378</v>
       </c>
       <c r="E49">
-        <v>-16.33290815033438</v>
+        <v>-14.33376348643422</v>
       </c>
       <c r="F49">
-        <v>-0.7970254409946913</v>
+        <v>-1.09938534158833</v>
       </c>
       <c r="G49">
-        <v>-2.824254034584898</v>
+        <v>-3.911533195502194</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.334754692264531</v>
       </c>
       <c r="E50">
-        <v>-14.28090260934268</v>
+        <v>-13.7983891753514</v>
       </c>
       <c r="F50">
-        <v>-1.064520185971902</v>
+        <v>-0.7923725012931665</v>
       </c>
       <c r="G50">
-        <v>-4.09797318863733</v>
+        <v>-4.583315717422182</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.409705812784834</v>
       </c>
       <c r="E51">
-        <v>-15.43852547687147</v>
+        <v>-13.08267291538711</v>
       </c>
       <c r="F51">
-        <v>-0.9539439064744044</v>
+        <v>-1.132792570575832</v>
       </c>
       <c r="G51">
-        <v>-3.493451020438715</v>
+        <v>-4.296168928982417</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.458538916628705</v>
       </c>
       <c r="E52">
-        <v>-13.42322774618595</v>
+        <v>-12.67839339835234</v>
       </c>
       <c r="F52">
-        <v>-0.6599571435882626</v>
+        <v>-0.5956385565978951</v>
       </c>
       <c r="G52">
-        <v>-2.608379981060102</v>
+        <v>-4.373225186954493</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.48017957937779</v>
       </c>
       <c r="E53">
-        <v>-11.99035969999694</v>
+        <v>-11.35056783524526</v>
       </c>
       <c r="F53">
-        <v>-0.4131724120484424</v>
+        <v>-0.9460595055345588</v>
       </c>
       <c r="G53">
-        <v>-3.505186904375431</v>
+        <v>-3.842574531919176</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.474146816265329</v>
       </c>
       <c r="E54">
-        <v>-13.40640446524745</v>
+        <v>-11.37542010059936</v>
       </c>
       <c r="F54">
-        <v>-0.9969568838647688</v>
+        <v>-1.104581690306092</v>
       </c>
       <c r="G54">
-        <v>-4.124467484588117</v>
+        <v>-4.367239720619491</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.441179222375307</v>
       </c>
       <c r="E55">
-        <v>-11.96077970777884</v>
+        <v>-10.88748608322089</v>
       </c>
       <c r="F55">
-        <v>-1.345090710402303</v>
+        <v>-1.457575548395851</v>
       </c>
       <c r="G55">
-        <v>-3.912605812256918</v>
+        <v>-4.994581479220303</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.382659186466038</v>
       </c>
       <c r="E56">
-        <v>-10.43937093779187</v>
+        <v>-8.953402005388927</v>
       </c>
       <c r="F56">
-        <v>-0.8965496426040379</v>
+        <v>-1.456361990150749</v>
       </c>
       <c r="G56">
-        <v>-4.893778678095035</v>
+        <v>-5.279391022509342</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.301378374917465</v>
       </c>
       <c r="E57">
-        <v>-11.60055318589069</v>
+        <v>-9.198030171283278</v>
       </c>
       <c r="F57">
-        <v>-0.8906690624115642</v>
+        <v>-1.282267326573989</v>
       </c>
       <c r="G57">
-        <v>-5.577783734146011</v>
+        <v>-5.315671291074215</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.200480908039132</v>
       </c>
       <c r="E58">
-        <v>-10.6263652149906</v>
+        <v>-8.996381752195726</v>
       </c>
       <c r="F58">
-        <v>-0.925123347796204</v>
+        <v>-1.254993329836815</v>
       </c>
       <c r="G58">
-        <v>-4.662719152181602</v>
+        <v>-5.060193181263118</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.083673085889879</v>
       </c>
       <c r="E59">
-        <v>-8.914986960381858</v>
+        <v>-7.565578690154223</v>
       </c>
       <c r="F59">
-        <v>-0.8877540375211127</v>
+        <v>-1.409824309461473</v>
       </c>
       <c r="G59">
-        <v>-5.014375230999605</v>
+        <v>-4.985705906629517</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.9567695372362792</v>
       </c>
       <c r="E60">
-        <v>-11.13371732891396</v>
+        <v>-7.380866763855357</v>
       </c>
       <c r="F60">
-        <v>-0.9193454851616775</v>
+        <v>-1.363941039020409</v>
       </c>
       <c r="G60">
-        <v>-5.129721258678892</v>
+        <v>-5.264122786482224</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.8247141069694174</v>
       </c>
       <c r="E61">
-        <v>-8.784485396428815</v>
+        <v>-7.00277994048095</v>
       </c>
       <c r="F61">
-        <v>-1.337695046230109</v>
+        <v>-1.560118320820999</v>
       </c>
       <c r="G61">
-        <v>-5.358741488540133</v>
+        <v>-5.761777234127625</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.691449380815532</v>
       </c>
       <c r="E62">
-        <v>-7.210016496493969</v>
+        <v>-6.276797629941277</v>
       </c>
       <c r="F62">
-        <v>-1.184788364082154</v>
+        <v>-1.561649143781372</v>
       </c>
       <c r="G62">
-        <v>-5.645848550433427</v>
+        <v>-6.251929985581039</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.5621364610551527</v>
       </c>
       <c r="E63">
-        <v>-9.606915146383852</v>
+        <v>-6.470951424546136</v>
       </c>
       <c r="F63">
-        <v>-1.247909131808073</v>
+        <v>-1.609046669834754</v>
       </c>
       <c r="G63">
-        <v>-5.262762152265583</v>
+        <v>-5.991161623998186</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.4397302068017339</v>
       </c>
       <c r="E64">
-        <v>-8.038201936912754</v>
+        <v>-5.743320749467671</v>
       </c>
       <c r="F64">
-        <v>-1.675418779616662</v>
+        <v>-1.489408879318033</v>
       </c>
       <c r="G64">
-        <v>-5.771116283093909</v>
+        <v>-6.543304340674453</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.3264851015662991</v>
       </c>
       <c r="E65">
-        <v>-7.5606652958559</v>
+        <v>-5.756969570126789</v>
       </c>
       <c r="F65">
-        <v>-1.642940150487699</v>
+        <v>-1.562875127537515</v>
       </c>
       <c r="G65">
-        <v>-6.243809217373206</v>
+        <v>-6.254952513658393</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.226458400985601</v>
       </c>
       <c r="E66">
-        <v>-8.524080027091738</v>
+        <v>-6.547446407483704</v>
       </c>
       <c r="F66">
-        <v>-1.391381537605545</v>
+        <v>-1.689293933613554</v>
       </c>
       <c r="G66">
-        <v>-5.211273237493298</v>
+        <v>-6.332511974552439</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.1424836855320726</v>
       </c>
       <c r="E67">
-        <v>-7.765012685452025</v>
+        <v>-5.10282244277079</v>
       </c>
       <c r="F67">
-        <v>-1.46797321603579</v>
+        <v>-1.845989568261914</v>
       </c>
       <c r="G67">
-        <v>-6.586245426864339</v>
+        <v>-6.990370341934252</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.07795185596730625</v>
       </c>
       <c r="E68">
-        <v>-7.780142317111652</v>
+        <v>-5.277372473396444</v>
       </c>
       <c r="F68">
-        <v>-1.841214030184775</v>
+        <v>-1.710867934252064</v>
       </c>
       <c r="G68">
-        <v>-6.60200693417681</v>
+        <v>-6.85111224382481</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.03742766084273181</v>
       </c>
       <c r="E69">
-        <v>-7.495052235958765</v>
+        <v>-6.652144726541042</v>
       </c>
       <c r="F69">
-        <v>-1.083695234611905</v>
+        <v>-1.554200464095399</v>
       </c>
       <c r="G69">
-        <v>-4.809296866478372</v>
+        <v>-7.262563396173129</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.02378376363225654</v>
       </c>
       <c r="E70">
-        <v>-6.765098453714364</v>
+        <v>-5.49336256966629</v>
       </c>
       <c r="F70">
-        <v>-1.178624482237923</v>
+        <v>-1.933049325561336</v>
       </c>
       <c r="G70">
-        <v>-7.093867927128487</v>
+        <v>-6.434927011355332</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.04038032869259311</v>
       </c>
       <c r="E71">
-        <v>-7.623366546966104</v>
+        <v>-5.408892944001215</v>
       </c>
       <c r="F71">
-        <v>-2.091281581741889</v>
+        <v>-1.914227161434926</v>
       </c>
       <c r="G71">
-        <v>-6.336262822648433</v>
+        <v>-5.749892375641641</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.09057832067669513</v>
       </c>
       <c r="E72">
-        <v>-7.675213045879922</v>
+        <v>-5.568308814493235</v>
       </c>
       <c r="F72">
-        <v>-1.672429201659958</v>
+        <v>-2.293812441521951</v>
       </c>
       <c r="G72">
-        <v>-5.431815160228466</v>
+        <v>-5.908573444429988</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.175559608836763</v>
       </c>
       <c r="E73">
-        <v>-7.607462546251166</v>
+        <v>-5.219050256651658</v>
       </c>
       <c r="F73">
-        <v>-2.031924087126888</v>
+        <v>-2.407600301440103</v>
       </c>
       <c r="G73">
-        <v>-4.417341516810821</v>
+        <v>-5.733760087228773</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.2958918172522707</v>
       </c>
       <c r="E74">
-        <v>-8.001584696086733</v>
+        <v>-5.801393900142036</v>
       </c>
       <c r="F74">
-        <v>-2.117979034766714</v>
+        <v>-2.523684395798814</v>
       </c>
       <c r="G74">
-        <v>-5.676818703953309</v>
+        <v>-5.419556210096545</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.4488418070728842</v>
       </c>
       <c r="E75">
-        <v>-7.777194280532658</v>
+        <v>-6.364595684001991</v>
       </c>
       <c r="F75">
-        <v>-1.9657648677675</v>
+        <v>-2.218281901734692</v>
       </c>
       <c r="G75">
-        <v>-4.909854687233735</v>
+        <v>-5.573387329669859</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.6288482531858792</v>
       </c>
       <c r="E76">
-        <v>-9.203337542820268</v>
+        <v>-5.963286845916251</v>
       </c>
       <c r="F76">
-        <v>-2.244512155544339</v>
+        <v>-2.451466497255351</v>
       </c>
       <c r="G76">
-        <v>-5.035145593712993</v>
+        <v>-5.486071691071581</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.8332508530923038</v>
       </c>
       <c r="E77">
-        <v>-9.83356979894176</v>
+        <v>-6.216107021290479</v>
       </c>
       <c r="F77">
-        <v>-2.639823990773513</v>
+        <v>-2.630011978887353</v>
       </c>
       <c r="G77">
-        <v>-3.769418096592361</v>
+        <v>-4.776539018367284</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.05843837014133</v>
       </c>
       <c r="E78">
-        <v>-9.397115474082492</v>
+        <v>-7.644120543343258</v>
       </c>
       <c r="F78">
-        <v>-2.258696290582475</v>
+        <v>-2.497576740364782</v>
       </c>
       <c r="G78">
-        <v>-5.10174714887205</v>
+        <v>-4.523841766809175</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.29919131591741</v>
       </c>
       <c r="E79">
-        <v>-10.90446786074965</v>
+        <v>-7.72081930761117</v>
       </c>
       <c r="F79">
-        <v>-2.416260882636372</v>
+        <v>-2.788833204291297</v>
       </c>
       <c r="G79">
-        <v>-3.819281533504864</v>
+        <v>-3.889590899667905</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.553857237828578</v>
       </c>
       <c r="E80">
-        <v>-9.720552673132332</v>
+        <v>-9.733879972136904</v>
       </c>
       <c r="F80">
-        <v>-2.67957982753607</v>
+        <v>-3.081989114672431</v>
       </c>
       <c r="G80">
-        <v>-3.018698926833991</v>
+        <v>-4.152395246757409</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.818418886943675</v>
       </c>
       <c r="E81">
-        <v>-10.71417685447334</v>
+        <v>-10.333771452407</v>
       </c>
       <c r="F81">
-        <v>-2.732038678420557</v>
+        <v>-2.728874314941863</v>
       </c>
       <c r="G81">
-        <v>-3.227365922719793</v>
+        <v>-3.817401143638557</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.086430379821156</v>
       </c>
       <c r="E82">
-        <v>-13.55437235344808</v>
+        <v>-10.09735793836257</v>
       </c>
       <c r="F82">
-        <v>-2.738914956231196</v>
+        <v>-2.990447889723863</v>
       </c>
       <c r="G82">
-        <v>-2.911013501532578</v>
+        <v>-3.277279017815385</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.355127989008894</v>
       </c>
       <c r="E83">
-        <v>-13.56357421263166</v>
+        <v>-11.57385783161547</v>
       </c>
       <c r="F83">
-        <v>-2.894078111184377</v>
+        <v>-3.347956350158879</v>
       </c>
       <c r="G83">
-        <v>-2.691189967179432</v>
+        <v>-2.778316904681971</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.618781922761118</v>
       </c>
       <c r="E84">
-        <v>-14.79088123819048</v>
+        <v>-12.38786009144223</v>
       </c>
       <c r="F84">
-        <v>-2.898108118598997</v>
+        <v>-3.475006372195851</v>
       </c>
       <c r="G84">
-        <v>-3.067224903348628</v>
+        <v>-3.224197730638711</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.868062919359868</v>
       </c>
       <c r="E85">
-        <v>-15.06073300430756</v>
+        <v>-13.29471871079628</v>
       </c>
       <c r="F85">
-        <v>-2.714045710064349</v>
+        <v>-3.441494768915597</v>
       </c>
       <c r="G85">
-        <v>-1.97813487402135</v>
+        <v>-2.309427787227296</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.096103673988515</v>
       </c>
       <c r="E86">
-        <v>-15.70295213112736</v>
+        <v>-15.0134647926155</v>
       </c>
       <c r="F86">
-        <v>-3.094976258813521</v>
+        <v>-3.430490736336808</v>
       </c>
       <c r="G86">
-        <v>-2.945926514789732</v>
+        <v>-1.644488162936982</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.293760095218178</v>
       </c>
       <c r="E87">
-        <v>-17.96288708465525</v>
+        <v>-16.21973252793468</v>
       </c>
       <c r="F87">
-        <v>-3.345820818994462</v>
+        <v>-3.453675083206361</v>
       </c>
       <c r="G87">
-        <v>-1.347429601152639</v>
+        <v>-1.858200430224633</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.449868231249908</v>
       </c>
       <c r="E88">
-        <v>-18.61600624841151</v>
+        <v>-17.59714035295174</v>
       </c>
       <c r="F88">
-        <v>-3.425321723743339</v>
+        <v>-3.550746488936018</v>
       </c>
       <c r="G88">
-        <v>-1.975721486323221</v>
+        <v>-1.455406354461508</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.555899864513939</v>
       </c>
       <c r="E89">
-        <v>-20.26248694201632</v>
+        <v>-18.3653235127689</v>
       </c>
       <c r="F89">
-        <v>-3.135596911144601</v>
+        <v>-3.760242261838818</v>
       </c>
       <c r="G89">
-        <v>-1.710093243888719</v>
+        <v>-1.564257091792745</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.603806473805308</v>
       </c>
       <c r="E90">
-        <v>-21.82840608302469</v>
+        <v>-21.71746299831077</v>
       </c>
       <c r="F90">
-        <v>-3.299787614053491</v>
+        <v>-3.90656425150192</v>
       </c>
       <c r="G90">
-        <v>-2.102624628480104</v>
+        <v>-1.299522696653846</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.586963186644087</v>
       </c>
       <c r="E91">
-        <v>-23.93496615038679</v>
+        <v>-22.51333777668483</v>
       </c>
       <c r="F91">
-        <v>-3.574272951542926</v>
+        <v>-3.973235401916238</v>
       </c>
       <c r="G91">
-        <v>-1.820291373254439</v>
+        <v>-1.608327074011523</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.502666511967347</v>
       </c>
       <c r="E92">
-        <v>-25.11003269979313</v>
+        <v>-24.28377638930161</v>
       </c>
       <c r="F92">
-        <v>-3.354633819792846</v>
+        <v>-4.208392340222962</v>
       </c>
       <c r="G92">
-        <v>-0.9895728705395808</v>
+        <v>-1.9080440038639</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.352506669691552</v>
       </c>
       <c r="E93">
-        <v>-27.90347623311268</v>
+        <v>-26.6186892869745</v>
       </c>
       <c r="F93">
-        <v>-3.854877439036842</v>
+        <v>-4.338265438368675</v>
       </c>
       <c r="G93">
-        <v>-1.494911094381631</v>
+        <v>-1.46198440844804</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.142095172461818</v>
       </c>
       <c r="E94">
-        <v>-30.40453431365299</v>
+        <v>-27.94394267684522</v>
       </c>
       <c r="F94">
-        <v>-4.015464743743554</v>
+        <v>-4.214386406749619</v>
       </c>
       <c r="G94">
-        <v>-2.521848941754632</v>
+        <v>-2.687432497992359</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.880991612670996</v>
       </c>
       <c r="E95">
-        <v>-31.28826828048686</v>
+        <v>-31.26337299462969</v>
       </c>
       <c r="F95">
-        <v>-3.809766207015187</v>
+        <v>-4.475061202899582</v>
       </c>
       <c r="G95">
-        <v>-2.724272248753369</v>
+        <v>-1.648606481587835</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.581657881830629</v>
       </c>
       <c r="E96">
-        <v>-32.48341634788021</v>
+        <v>-32.56062230123698</v>
       </c>
       <c r="F96">
-        <v>-3.896699224101981</v>
+        <v>-4.567294114629487</v>
       </c>
       <c r="G96">
-        <v>-2.600421429583694</v>
+        <v>-2.6797056847037</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.262139926342353</v>
       </c>
       <c r="E97">
-        <v>-36.4877647739028</v>
+        <v>-34.29206848841072</v>
       </c>
       <c r="F97">
-        <v>-4.423314747981502</v>
+        <v>-4.658921489787946</v>
       </c>
       <c r="G97">
-        <v>-2.614315789212015</v>
+        <v>-3.084135169963225</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.936079468941079</v>
       </c>
       <c r="E98">
-        <v>-38.19302958860119</v>
+        <v>-36.79279146187446</v>
       </c>
       <c r="F98">
-        <v>-4.374693723274185</v>
+        <v>-4.813069066305295</v>
       </c>
       <c r="G98">
-        <v>-4.066963308570977</v>
+        <v>-3.554755702734939</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.625555629841185</v>
       </c>
       <c r="E99">
-        <v>-40.97315487986418</v>
+        <v>-38.92027987186301</v>
       </c>
       <c r="F99">
-        <v>-4.606343353997456</v>
+        <v>-5.112914043464035</v>
       </c>
       <c r="G99">
-        <v>-3.783650131865688</v>
+        <v>-3.875934899318411</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.340331607149898</v>
       </c>
       <c r="E100">
-        <v>-43.20140636499741</v>
+        <v>-41.39844198782054</v>
       </c>
       <c r="F100">
-        <v>-4.46085470194157</v>
+        <v>-5.090482682563627</v>
       </c>
       <c r="G100">
-        <v>-4.243623950183105</v>
+        <v>-4.941592887318728</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.105031522138924</v>
       </c>
       <c r="E101">
-        <v>-44.28804087398196</v>
+        <v>-43.25969461818714</v>
       </c>
       <c r="F101">
-        <v>-4.518821367687271</v>
+        <v>-4.881629722765399</v>
       </c>
       <c r="G101">
-        <v>-4.481877291553374</v>
+        <v>-4.87639831401386</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.9103990147553843</v>
       </c>
       <c r="E102">
-        <v>-47.35604125791256</v>
+        <v>-46.15249060699797</v>
       </c>
       <c r="F102">
-        <v>-4.805289039658202</v>
+        <v>-4.805786060099882</v>
       </c>
       <c r="G102">
-        <v>-4.535077758369462</v>
+        <v>-5.011607614928774</v>
       </c>
     </row>
   </sheetData>
